--- a/data/dividends_info_20260801.xlsx
+++ b/data/dividends_info_20260801.xlsx
@@ -710,8 +710,12 @@
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>45.67499923706055</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1970443382667302</v>
+      </c>
       <c r="J6" t="n">
         <v>135</v>
       </c>
@@ -1176,8 +1180,12 @@
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>45.67499923706055</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1970443382667302</v>
+      </c>
       <c r="J16" t="n">
         <v>51</v>
       </c>
@@ -1407,8 +1415,12 @@
           <t>IT0005187460</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>5.159999847412109</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.7364341303044438</v>
+      </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
@@ -3575,61 +3587,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Vimi Fasteners S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>